--- a/Result/profitability/2596.xlsx
+++ b/Result/profitability/2596.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>25.6075</v>
+        <v>29.64</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -680,7 +680,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -777,7 +777,7 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>28.55375</v>
+        <v>30.5725</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>29.02375</v>
+        <v>31.28</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>31.44</v>
+        <v>33.815</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>32.81</v>
+        <v>37.79875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>36.79875</v>
+        <v>38.12125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>37.18</v>
+        <v>37.825</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
         <v>0.5649999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>37.36</v>
+        <v>37.36000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9808,6 +9808,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2596</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>619</v>
+      </c>
+      <c r="D75" t="n">
+        <v>350</v>
+      </c>
+      <c r="E75" t="n">
+        <v>270</v>
+      </c>
+      <c r="F75" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="G75" t="n">
+        <v>216</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>34.82%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>223</v>
+      </c>
+      <c r="K75" t="n">
+        <v>181</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6012500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.91125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X75" t="n">
+        <v>8.049999999999999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.159999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1344100026048449</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.661764705882353</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.7739307535641546</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
